--- a/Budget_DanceYourFoot_2027.xlsx
+++ b/Budget_DanceYourFoot_2027.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot; CHF&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,12 +31,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00F5B731"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00BBBBBB"/>
+      <color rgb="00AAAAAA"/>
       <sz val="10"/>
     </font>
     <font>
@@ -53,17 +53,36 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00333333"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A0A12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A6B2A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="008B3A00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -72,19 +91,25 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00F5B731"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00C41E3A"/>
-      <sz val="10"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00F5B731"/>
-      <sz val="14"/>
+      <color rgb="007B5800"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A3A6B"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -94,12 +119,23 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <b val="1"/>
+      <color rgb="00F5B731"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -123,7 +159,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F7F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5EA"/>
       </patternFill>
     </fill>
     <fill>
@@ -133,7 +174,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007B3A8F"/>
+        <fgColor rgb="00FFF0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A3A6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A6B5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -143,69 +204,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF0E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="005C2D8F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="006B1D3A"/>
-      </left>
-      <right style="thin">
-        <color rgb="006B1D3A"/>
-      </right>
-      <top style="thin">
-        <color rgb="006B1D3A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="006B1D3A"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00C41E3A"/>
-      </left>
-      <right style="medium">
-        <color rgb="00C41E3A"/>
-      </right>
-      <top style="medium">
-        <color rgb="00C41E3A"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00C41E3A"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00DDDDDD"/>
-      </left>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
     </border>
     <border>
       <left style="medium">
@@ -222,38 +246,24 @@
       </bottom>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="007B3A8F"/>
+      <left style="thin">
+        <color rgb="00E0E0E0"/>
       </left>
-      <right style="medium">
-        <color rgb="007B3A8F"/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
       </right>
-      <top style="medium">
-        <color rgb="007B3A8F"/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
       </top>
-      <bottom style="medium">
-        <color rgb="007B3A8F"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="00E86A17"/>
-      </left>
-      <right style="medium">
-        <color rgb="00E86A17"/>
-      </right>
-      <top style="medium">
-        <color rgb="00E86A17"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00E86A17"/>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -264,63 +274,102 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,31 +737,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="48" customHeight="1">
+    <row r="1" ht="52" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DANCE YOUR FOOT · BUDGET ÉDITION 2027</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Suisse romande · Première édition · Contact : Sylvain@danceyourfoot.com</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>POSTE</t>
@@ -734,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="26" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>👥  RH &amp; CACHETS</t>
@@ -747,35 +796,35 @@
           <t>Coordination</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Responsable événement — journée complète</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>DJ</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Cachet artiste (tarif à revoir : +300 CHF min.)</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Cachet artiste — tarif estimé marché suisse</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>À négocier</t>
         </is>
@@ -787,35 +836,35 @@
           <t>MC / Speaker</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Animation publique — cachet</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>À négocier</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Arbitre</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Match officiel, briefing inclus</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
@@ -827,456 +876,607 @@
           <t>Photo &amp; vidéo</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Captation jour J + traitement + montage</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Captation jour J + traitement + montage inclus</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Défraiements équipes</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>4 équipes × 200 CHF</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>4 équipes × 200 CHF (transport, repas)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="n">
         <v>800</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Sous-total  RH &amp; CACHETS</t>
-        </is>
-      </c>
-      <c r="C12" s="10">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Sous-total — RH &amp; CACHETS</t>
+        </is>
+      </c>
+      <c r="C12" s="14">
         <f>SUM(C6:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="11" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>📦  MATÉRIEL &amp; LOGISTIQUE</t>
+      <c r="D12" s="15" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>🏟️  LIEU &amp; TECHNIQUE</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Ballon personnalisé</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Ballon officiel aux couleurs DYF</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Confirmé</t>
+          <t>Location salle / lieu</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Espace urbain couvert — estimation milieu de gamme</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Chasubles personnalisées</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>30 pièces — crew + équipes</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>400</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Confirmé</t>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Sonorisation</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Enceintes, table de mix, câblage, ingé son</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>Éclairage</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Jeux de lumière, projecteurs, ambiance scénique</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Électricité</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Raccordement technique / générateur si besoin</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Sous-total — LIEU &amp; TECHNIQUE</t>
+        </is>
+      </c>
+      <c r="C19" s="14">
+        <f>SUM(C15:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="15" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>📦  MATÉRIEL &amp; LOGISTIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>Terrain gonflable</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Location + installation + personnalisation</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C22" s="7" t="n">
         <v>2000</v>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Chasubles personnalisées</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>30 pièces — crew + équipes</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Ballon personnalisé</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Ballon officiel aux couleurs DYF</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Cartons public &amp; arbitres</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>~500 cartons bicolores distribués à l'entrée</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Transport &amp; logistique</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Déplacement matériel, manutention</t>
         </is>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C26" s="7" t="n">
         <v>300</v>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Cartons public &amp; arbitres</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>~500 cartons bicolores</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Sous-total — MATÉRIEL &amp; LOGISTIQUE</t>
+        </is>
+      </c>
+      <c r="C27" s="14">
+        <f>SUM(C22:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="15" t="n"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>🛡️  SÉCURITÉ &amp; COUVERTURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Sécurité / Service d'ordre</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Agent(s) selon exigences du lieu</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Assurance événementielle</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>RC obligatoire pour location de salle</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>SUISA</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Droits musique live — selon nb spectateurs</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>À vérifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Sous-total — SÉCURITÉ &amp; COUVERTURE</t>
+        </is>
+      </c>
+      <c r="C33" s="14">
+        <f>SUM(C30:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="15" t="n"/>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>📣  COMMUNICATION &amp; RÉCOMPENSES</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Affiches, flyers, impression + boost réseaux sociaux</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Trophées / Prix</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Récompenses équipes, MVP, mention spéciale DJ</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Badges &amp; accréditations</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Staff, presse, sponsors — impression + cordons</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Sous-total — COMMUNICATION &amp; RÉCOMPENSES</t>
+        </is>
+      </c>
+      <c r="C39" s="14">
+        <f>SUM(C36:C38)</f>
+        <v/>
+      </c>
+      <c r="D39" s="15" t="n"/>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>🎨  ORGANISATION &amp; ADMINISTRATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Organisation générale</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Frais admin, coordination, réunions</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Sous-total  MATÉRIEL &amp; LOGISTIQUE</t>
-        </is>
-      </c>
-      <c r="C20" s="10">
-        <f>SUM(C15:C19)</f>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Création graphique &amp; tech</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Identité visuelle, supports, site web</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Divers &amp; imprévus</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Réserve ~5% du budget total</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>Réserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>Sous-total — ORGANISATION &amp; ADMINISTRATION</t>
+        </is>
+      </c>
+      <c r="C45" s="14">
+        <f>SUM(C42:C44)</f>
         <v/>
       </c>
-      <c r="D20" s="11" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>🎨  ORGANISATION &amp; COMMUNICATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>SUISA</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Droits musique live — Suisse (selon nb spectateurs)</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>200</v>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D45" s="15" t="n"/>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="29" t="inlineStr">
+        <is>
+          <t>💰  TOTAL GÉNÉRAL</t>
+        </is>
+      </c>
+      <c r="C48" s="30">
+        <f>C12+C19+C27+C33+C39+C45</f>
+        <v/>
+      </c>
+      <c r="D48" s="15" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>Légende des statuts :</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+      <c r="B51" s="33" t="inlineStr">
+        <is>
+          <t>Montant validé</t>
+        </is>
+      </c>
+      <c r="C51" s="34" t="n"/>
+      <c r="D51" s="34" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="35" t="inlineStr">
+        <is>
+          <t>Estimé</t>
+        </is>
+      </c>
+      <c r="B52" s="33" t="inlineStr">
+        <is>
+          <t>Montant ajouté par DYF</t>
+        </is>
+      </c>
+      <c r="C52" s="34" t="n"/>
+      <c r="D52" s="34" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="36" t="inlineStr">
+        <is>
+          <t>À négocier</t>
+        </is>
+      </c>
+      <c r="B53" s="33" t="inlineStr">
+        <is>
+          <t>Tarif à confirmer</t>
+        </is>
+      </c>
+      <c r="C53" s="34" t="n"/>
+      <c r="D53" s="34" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="37" t="inlineStr">
         <is>
           <t>À vérifier</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Organisation générale</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Frais admin, imprévus ops</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Confirmé</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Création graphique &amp; tech</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Identité visuelle, supports, site</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Confirmé</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>Divers &amp; imprévus</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Réserve 5 %</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>500</v>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="B54" s="33" t="inlineStr">
+        <is>
+          <t>Dépend du contexte</t>
+        </is>
+      </c>
+      <c r="C54" s="34" t="n"/>
+      <c r="D54" s="34" t="n"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="38" t="inlineStr">
         <is>
           <t>Réserve</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Sous-total  ORGANISATION &amp; COMMUNICATION</t>
-        </is>
-      </c>
-      <c r="C27" s="10">
-        <f>SUM(C23:C26)</f>
-        <v/>
-      </c>
-      <c r="D27" s="11" t="n"/>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>⚠️  POSTES MANQUANTS (à budgéter)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Location salle / lieu</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Estimation : 1 500–5 000 CHF selon lieu</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>Sonorisation</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>Enceintes, table de mix, câblage DJ — 500–1 500</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>Éclairage</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>Jeux de lumière, projecteurs — 300–800</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>Assurance événementielle</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>RC obligatoire pour la plupart des salles</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>Trophées / Prix</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>Récompenses équipes + MVP — 200–500</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>Communication</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>Affiches, flyers, boost réseaux — 300–600</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Sécurité</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>Souvent exigé selon le lieu — 300–800</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>Non budgété</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>💰  TOTAL BUDGETÉ (hors postes manquants)</t>
-        </is>
-      </c>
-      <c r="C39" s="22">
-        <f>C12+C20+C27</f>
-        <v/>
-      </c>
-      <c r="D39" s="11" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>ℹ️  Budget réaliste estimé avec tous les postes manquants comblés : 15 000 – 18 000 CHF</t>
-        </is>
-      </c>
+      <c r="B55" s="33" t="inlineStr">
+        <is>
+          <t>Tampon imprévus</t>
+        </is>
+      </c>
+      <c r="C55" s="34" t="n"/>
+      <c r="D55" s="34" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="16">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="A2:D2"/>
